--- a/tests/referral/data/result_conf_init_permuted.xlsx
+++ b/tests/referral/data/result_conf_init_permuted.xlsx
@@ -407,7 +407,7 @@
         <v>73</v>
       </c>
       <c r="F2">
-        <v>704</v>
+        <v>721</v>
       </c>
     </row>
     <row r="3">
@@ -428,10 +428,10 @@
         </is>
       </c>
       <c r="E3">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F3">
-        <v>650</v>
+        <v>634</v>
       </c>
     </row>
   </sheetData>

--- a/tests/referral/data/result_conf_init_permuted.xlsx
+++ b/tests/referral/data/result_conf_init_permuted.xlsx
@@ -428,10 +428,10 @@
         </is>
       </c>
       <c r="E3">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F3">
-        <v>634</v>
+        <v>661</v>
       </c>
     </row>
   </sheetData>
